--- a/DGK_32616403815.xlsx
+++ b/DGK_32616403815.xlsx
@@ -69248,7 +69248,8 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -69278,7 +69279,8 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (служба продаж); приёмная 8 800 222-15-44</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -69308,12 +69310,13 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57 (Москва); Алексин +7 (48753) 2-70-25, 2-61-13 (по armtorg.ru)</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>office@aztpa.ru; ngskr@aztpa.ru (клиновые задвижки)</t>
+          <t>office@ogscomp.ru (указан на aztpa.ru)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -69338,7 +69341,8 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10; отдел продаж (34766) 2-11-74, 2-13-57 (по ibprom.ru)</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -69368,7 +69372,8 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97; +7 (812) 334-92-39</t>
+          <t>+7 (812) 458-55-97; +7 (812) 334-92-39
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -69398,7 +69403,8 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -69428,12 +69434,13 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте
+[semlmz.ru — контакты на сайте не опубликованы; не звонить, искать через дилеров]</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -69458,7 +69465,8 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -69488,7 +69496,8 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>8 (495) 925-51-64</t>
+          <t>8 (495) 925-51-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -69524,7 +69533,8 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -69554,7 +69564,8 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67</t>
+          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -69584,7 +69595,8 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -69614,12 +69626,13 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>8-800-700-77-85; +7 (495) 792-11-05
+[сайт teplo-sila.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>marketing@teplo-sila.com</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -69644,7 +69657,8 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -69674,7 +69688,8 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -69704,7 +69719,8 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -69734,7 +69750,8 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -69764,7 +69781,8 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -69794,12 +69812,13 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+7 (991) 210-60-21</t>
+          <t>8-800-200-52-76; +7 (991) 210-60-21
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>reklama@pik-algrupp.ru (общий)</t>
+          <t>sales@pik-algrupp.ru</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -69824,7 +69843,8 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -69860,12 +69880,13 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47 (пн-пт 8:30-17:30)</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>office@chsgs.ru; 166@ldtd.ru</t>
+          <t>office@chsgs.ru</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -69890,7 +69911,8 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -69920,7 +69942,8 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8-800-444-74-74; +7 900 093-04-01</t>
+          <t>8-800-444-74-74; +7 (351) 246-02-10; +7 (351) 245-02-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -69950,7 +69973,8 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>+7 (749) 527-55-88 (как в каталоге productcenter — уточнить номер)</t>
+          <t>+7 (495) 275-58-88
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -69980,7 +70004,8 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -70010,7 +70035,8 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -70040,7 +70066,8 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -70070,7 +70097,8 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -70100,7 +70128,8 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77; 8-800-775-74-84</t>
+          <t>+7 (812) 611-03-77; 8-800-775-74-84
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -70130,12 +70159,13 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>+7 (812) 325-90-51; +7 (495) 666-33-01</t>
+          <t>+7 (812) 325-90-51; +7 (495) 666-33-01
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>info@rosma.spb.ru (уточнить)</t>
+          <t>info@rosma.spb.ru</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -70166,7 +70196,8 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -70196,7 +70227,8 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (495) 668-10-92; +7 (8412) 35-07-97; +7 (812) 309-54-81
+[сайт promarm.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -70226,7 +70258,8 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)</t>
+          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -70256,12 +70289,13 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (351) 307-71-09
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>info@zaoutk.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -70292,7 +70326,8 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>+7 (4872) 72-47-16 (отдел реализации)</t>
+          <t>+7 (4872) 72-47-16 (отдел реализации)
+[сайт tulaprivod.ru не открылся 22.10 — проверить звонком]</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -70322,7 +70357,8 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>(8352) 305-148, 305-221</t>
+          <t>+7 (8352) 30-51-48; 30-52-21; Москва +7 (495) 735-42-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -70352,7 +70388,8 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41</t>
+          <t>(49241) 2-32-41
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -70382,7 +70419,8 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (499) 653-65-06
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -70412,7 +70450,8 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>(8453) 75-48-28, 75-48-82</t>
+          <t>(8453) 75-48-28, 75-48-82
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -70442,7 +70481,8 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[консультация, не поставщик]</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
